--- a/data_raw/re_A030A_住宅商品房销售面积_万平方米.xlsx
+++ b/data_raw/re_A030A_住宅商品房销售面积_万平方米.xlsx
@@ -1,216 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>住宅商品房销售面积(万平方米)</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>乌鲁木齐</t>
-  </si>
-  <si>
-    <t>兰州</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>南京</t>
-  </si>
-  <si>
-    <t>南宁</t>
-  </si>
-  <si>
-    <t>南昌</t>
-  </si>
-  <si>
-    <t>厦门</t>
-  </si>
-  <si>
-    <t>合肥</t>
-  </si>
-  <si>
-    <t>呼和浩特</t>
-  </si>
-  <si>
-    <t>哈尔滨</t>
-  </si>
-  <si>
-    <t>大连</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
-    <t>太原</t>
-  </si>
-  <si>
-    <t>宁波</t>
-  </si>
-  <si>
-    <t>广州</t>
-  </si>
-  <si>
-    <t>成都</t>
-  </si>
-  <si>
-    <t>拉萨</t>
-  </si>
-  <si>
-    <t>昆明</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>沈阳</t>
-  </si>
-  <si>
-    <t>济南</t>
-  </si>
-  <si>
-    <t>海口</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>石家庄</t>
-  </si>
-  <si>
-    <t>福州</t>
-  </si>
-  <si>
-    <t>西宁</t>
-  </si>
-  <si>
-    <t>西安</t>
-  </si>
-  <si>
-    <t>贵阳</t>
-  </si>
-  <si>
-    <t>郑州</t>
-  </si>
-  <si>
-    <t>重庆</t>
-  </si>
-  <si>
-    <t>银川</t>
-  </si>
-  <si>
-    <t>长春</t>
-  </si>
-  <si>
-    <t>长沙</t>
-  </si>
-  <si>
-    <t>青岛</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -541,2251 +420,2424 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>住宅商品房销售面积(万平方米)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>2615.4915</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>3279.1745</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>2007.48</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>2928.04</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1690.82</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>1499.9998</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>1592.6284</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>2015.8086</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>1780.9092</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>2009.1663</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>2019.7967</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>1341.6197</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>1333.2914</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>1353.6992</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>1434.0696</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>1489.946</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>1561.5112</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>1456.9583</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>1356.729</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>381.9029</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>468.08</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>265.06</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>505.57</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>405.3</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>421.507</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>337.2962</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>488.5382</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>401.7521</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>465.4066</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>519.6594</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>525.9742</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>509.2802</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>566.8474</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>636.8411</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>703.0623000000001</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>421.072</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="n">
         <v>497.9278</v>
       </c>
-      <c r="T3">
+      <c r="T3" t="n">
         <v>348.5622</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4">
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>195.183</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>255.2822</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>134.05</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>224.68</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>206.81</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>118.1286</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>176.7479</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>237.3499</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>439.4287</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>578.6186</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>713.9217</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>609.3968</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>565.9266</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>673.4834</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>796.7885</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>761.5444</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>259.1631</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="n">
         <v>315.2239</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="n">
         <v>284.961</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5">
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>2205.0296</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1731.4798</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>1031.43</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>1880.45</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>1201.39</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>1034.9608</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>1483.3746</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>1363.6732</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>1136.5281</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>1126.8399</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>981.366</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>608.7804</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>526.7602000000001</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>789.0165</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>733.5942</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>877.1015</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>741.9329</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="n">
         <v>818.2508</v>
       </c>
-      <c r="T5">
+      <c r="T5" t="n">
         <v>785.7211</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>940.9934</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1064.5159</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>659.12</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1114.03</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>754.8200000000001</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>680.8946999999999</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>876.2538</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>1143.1541</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>1124.7311</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>1429.1841</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>1406.2893</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>1208.9774</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>982.6521</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>1137.1912</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>1213.8139</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>1371.3888</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>791.9632</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="n">
         <v>797.083</v>
       </c>
-      <c r="T6">
+      <c r="T6" t="n">
         <v>831.6887</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>419.7888</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>585.4733</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>454.66</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>685.08</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>604.75</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>612.2415999999999</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>575.5204</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>633.1392</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>720.9514</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>878.8674999999999</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>1150.1526</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>1307.6791</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>1438.2453</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>1550.3301</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>1486.1899</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>1125.5128</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>678.5191</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>574.7429</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>470.5679</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>359.9864</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>460.3378</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>326.46</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>463.63</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>489.3</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>436.0131</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>595.333</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>751.8728</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>751.4757</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>815.9902</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>1077.8161</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>1289.7947</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>1536.5198</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>1580.8859</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>1367.2444</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>1562.2908</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>1056.8778</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>548.1708</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>568.3491</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>317.386</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>369.557</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>150.21</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>401.3</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>238.68</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>272.1301</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>480.2694</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>581.5237</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>510.3704</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>345.8945</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>322.3391</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>237.2751</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>170.6813</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>274.7007</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>379.1347</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>413.2404</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>394.95</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>346.7348</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>362.1914</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>583.255</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>953.103</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>867.35</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>1180.33</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>863.65</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1058.3953</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>1117.3264</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>1451.6915</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>1326.2153</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>1285.8981</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>1705.7175</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>960.4586</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>1103.8785</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>1155.7207</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>1297.4015</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>1562.7581</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>1237.8281</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>937.6061999999999</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>793.8808</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>193.8545</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>213.3251</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>308.14</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>312.6</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>394.75</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>408.3908</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>414.3054</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>339.9637</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>306.9181</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>321.4363</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>344.8005</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>249.9733</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>342.4324</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>296.2751</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>382.2666</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>264.0493</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>137.3055</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>180.4257</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>169.8324</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12">
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>575.2259</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>667.8136</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>504.56</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>627.8200000000001</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>809.91</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>920.0171</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>1031.6131</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>1226.9961</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>919.8093</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>807.2336</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>908.1553</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>1089.162</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>920.0014</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>824.7752</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>679.3244999999999</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>517.0669</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>359.2064</v>
       </c>
-      <c r="S12">
+      <c r="S12" t="n">
         <v>343.0537</v>
       </c>
-      <c r="T12">
+      <c r="T12" t="n">
         <v>274.577</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>570.2064</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>783.9121</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>770.84</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>1093.41</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>1126.68</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>833.4237000000001</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>966.8943</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>1104.0202</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>670.7348</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>596.6703</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>654.6159</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>758.1734</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>702.0868</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>602.7439000000001</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>629.0807</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>627.2441</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>386.9882</v>
       </c>
-      <c r="S13">
+      <c r="S13" t="n">
         <v>266.7449</v>
       </c>
-      <c r="T13">
+      <c r="T13" t="n">
         <v>266.8992</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14">
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>1332.4916</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>1401.8481</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>1135.35</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>1461.47</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>1302.61</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>1365.7081</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>1511.4032</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>1720.3433</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>1483.6367</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>1674.7843</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>2521.8725</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>1342.869</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>1140.7314</v>
       </c>
-      <c r="O14">
+      <c r="O14" t="n">
         <v>1382.6264</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="n">
         <v>1220.74</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" t="n">
         <v>1333.9667</v>
       </c>
-      <c r="R14">
+      <c r="R14" t="n">
         <v>895.535</v>
       </c>
-      <c r="S14">
+      <c r="S14" t="n">
         <v>1110.2536</v>
       </c>
-      <c r="T14">
+      <c r="T14" t="n">
         <v>1108.3933</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15">
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>124.8376</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>149.0292</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>162.11</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>168.83</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>235.49</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>191.8873</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>308.1279</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>401.145</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>394.0938</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>421.6484</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>556.4448</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>722.1024</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>771.2139</v>
       </c>
-      <c r="O15">
+      <c r="O15" t="n">
         <v>645.4789</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="n">
         <v>701.2369</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" t="n">
         <v>728.2599</v>
       </c>
-      <c r="R15">
+      <c r="R15" t="n">
         <v>468.7448</v>
       </c>
-      <c r="S15">
+      <c r="S15" t="n">
         <v>511.3168</v>
       </c>
-      <c r="T15">
+      <c r="T15" t="n">
         <v>376.7489</v>
       </c>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>512.6296</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>657.9517</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>357.08</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>651.97</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>497.81</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>342.6513</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>458.7421</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>581.9535</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>595.1952</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>846.9217</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>1126.0593</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>1283.7186</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>1299.1718</v>
       </c>
-      <c r="O16">
+      <c r="O16" t="n">
         <v>1438.8911</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>1571.439</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" t="n">
         <v>1280.7968</v>
       </c>
-      <c r="R16">
+      <c r="R16" t="n">
         <v>835.1535</v>
       </c>
-      <c r="S16">
+      <c r="S16" t="n">
         <v>730.4553</v>
       </c>
-      <c r="T16">
+      <c r="T16" t="n">
         <v>637.0201</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>1156.3264</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>1158.6291</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>879.48</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>1253.6</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>1111.66</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>991.6709</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>1128.5112</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>1398.466</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>1196.229</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>1344.8608</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>1624.0052</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>1367.4778</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>1138.1986</v>
       </c>
-      <c r="O17">
+      <c r="O17" t="n">
         <v>1106.5763</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>1223.2059</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" t="n">
         <v>1371.0144</v>
       </c>
-      <c r="R17">
+      <c r="R17" t="n">
         <v>1026.5306</v>
       </c>
-      <c r="S17">
+      <c r="S17" t="n">
         <v>1067.705</v>
       </c>
-      <c r="T17">
+      <c r="T17" t="n">
         <v>846.4766</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>1482.1751</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>2084.8008</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>1357.43</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>2547.59</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>2289.92</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>2284.9102</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>2424.6051</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>2555.8054</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>2476.2538</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>2447.1272</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>3279.1714</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>2976.4694</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>2660.0222</v>
       </c>
-      <c r="O18">
+      <c r="O18" t="n">
         <v>2564.862</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="n">
         <v>2826.7431</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" t="n">
         <v>2614.4784</v>
       </c>
-      <c r="R18">
+      <c r="R18" t="n">
         <v>1885.6131</v>
       </c>
-      <c r="S18">
+      <c r="S18" t="n">
         <v>1786.1881</v>
       </c>
-      <c r="T18">
+      <c r="T18" t="n">
         <v>1387.3908</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>841.6654</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>862.2731</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>521.45</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>782.54</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>1095.95</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>934.8861000000001</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>917.7307</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>1041.3531</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>978.2294000000001</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>1008.2457</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>1128.8934</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>1387.7657</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>1430.1676</v>
       </c>
-      <c r="O20">
+      <c r="O20" t="n">
         <v>1484.8386</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>1527.0971</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" t="n">
         <v>965.1651000000001</v>
       </c>
-      <c r="R20">
+      <c r="R20" t="n">
         <v>603.1021</v>
       </c>
-      <c r="S20">
+      <c r="S20" t="n">
         <v>528.876</v>
       </c>
-      <c r="T20">
+      <c r="T20" t="n">
         <v>480.9236</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>679.9579</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>1043.6698</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>676.99</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>1314.38</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>797.59</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>600.2035</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>920.2569</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>968.776</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>952.5062</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>1292.3545</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>1888.2848</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>1520.1684</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>1329.4032</v>
       </c>
-      <c r="O21">
+      <c r="O21" t="n">
         <v>1284.2709</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="n">
         <v>1471.6177</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" t="n">
         <v>1954.3019</v>
       </c>
-      <c r="R21">
+      <c r="R21" t="n">
         <v>1168.2181</v>
       </c>
-      <c r="S21">
+      <c r="S21" t="n">
         <v>1202.1574</v>
       </c>
-      <c r="T21">
+      <c r="T21" t="n">
         <v>840.2817</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22">
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>908.923</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>1069.8933</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>683.24</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>1041.39</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1095.22</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>1182.207</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>1390.4712</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>1750.4293</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>1978.963</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>2413.769</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>2931.0559</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>3085.775</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>3229.7547</v>
       </c>
-      <c r="O22">
+      <c r="O22" t="n">
         <v>2981.7857</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>2252.3928</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" t="n">
         <v>2470.5345</v>
       </c>
-      <c r="R22">
+      <c r="R22" t="n">
         <v>1742.424</v>
       </c>
-      <c r="S22">
+      <c r="S22" t="n">
         <v>1583.9635</v>
       </c>
-      <c r="T22">
+      <c r="T22" t="n">
         <v>1583.5057</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23">
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>1150.6491</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>1358.1077</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>1307.18</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>1369.31</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1516.06</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>1947.7841</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>2201.4548</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>2017.3699</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>1342.3812</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>949.8845</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>1099.3885</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>1191.2477</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>1202.6733</v>
       </c>
-      <c r="O23">
+      <c r="O23" t="n">
         <v>1361.1283</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="n">
         <v>1285.5</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" t="n">
         <v>985.0801</v>
       </c>
-      <c r="R23">
+      <c r="R23" t="n">
         <v>594.8531</v>
       </c>
-      <c r="S23">
+      <c r="S23" t="n">
         <v>461.2157</v>
       </c>
-      <c r="T23">
+      <c r="T23" t="n">
         <v>468.4194</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24">
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>256.8392</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>290.7868</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>330.04</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>404.31</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>477.31</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>538.8986</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>559.9195</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>705.3072</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>723.9161</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>924.4318</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>1232.7168</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>974.7214</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>965.2943</v>
       </c>
-      <c r="O24">
+      <c r="O24" t="n">
         <v>934.0012</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="n">
         <v>1145.2394</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" t="n">
         <v>1300.1987</v>
       </c>
-      <c r="R24">
+      <c r="R24" t="n">
         <v>907.0928</v>
       </c>
-      <c r="S24">
+      <c r="S24" t="n">
         <v>825.5244</v>
       </c>
-      <c r="T24">
+      <c r="T24" t="n">
         <v>691.0806</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25">
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>海口</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>133.476</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>162.394</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>168.42</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>183.39</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>199.7</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>193.1647</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>251.4881</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>319.039</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>297.5829</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>330.2847</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>394.3338</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>487.3748</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>331.4394</v>
       </c>
-      <c r="O25">
+      <c r="O25" t="n">
         <v>373.4911</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="n">
         <v>371.5246</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" t="n">
         <v>349.0947</v>
       </c>
-      <c r="R25">
+      <c r="R25" t="n">
         <v>205.6698</v>
       </c>
-      <c r="S25">
+      <c r="S25" t="n">
         <v>263.351</v>
       </c>
-      <c r="T25">
+      <c r="T25" t="n">
         <v>327.5879</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26">
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>686.1814000000001</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>500.3483</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>413.65</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>717.39</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>413.8</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>469.4316</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>488.4429</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>527.1586</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>474.8091</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>747.8298</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>660.0848999999999</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>520.9653</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>572.9894</v>
       </c>
-      <c r="O26">
+      <c r="O26" t="n">
         <v>638.4224</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="n">
         <v>752.2714</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" t="n">
         <v>623.3003</v>
       </c>
-      <c r="R26">
+      <c r="R26" t="n">
         <v>489.9823</v>
       </c>
-      <c r="S26">
+      <c r="S26" t="n">
         <v>584.3316</v>
       </c>
-      <c r="T26">
+      <c r="T26" t="n">
         <v>656.944</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27">
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>287.9642</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>381.5587</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>326.4</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>329.14</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>446.43</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>783.2012999999999</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>697.0793</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>782.7284</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>725.6840999999999</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>539.6783</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>652.5212</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>816.936</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>723.9014</v>
       </c>
-      <c r="O27">
+      <c r="O27" t="n">
         <v>673.9433</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="n">
         <v>617.9974</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" t="n">
         <v>677.5232999999999</v>
       </c>
-      <c r="R27">
+      <c r="R27" t="n">
         <v>567.9053</v>
       </c>
-      <c r="S27">
+      <c r="S27" t="n">
         <v>565.9265</v>
       </c>
-      <c r="T27">
+      <c r="T27" t="n">
         <v>466.9867</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28">
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>621.4163</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>592.5304</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>341.44</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>648.28</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>531.1</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>532.0029</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>733.9564</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>1105.4793</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>816.6525</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>748.9896</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>1021.2284</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>1276.8001</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>1255.6766</v>
       </c>
-      <c r="O28">
+      <c r="O28" t="n">
         <v>1330.0731</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="n">
         <v>1519.1725</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" t="n">
         <v>1686.2559</v>
       </c>
-      <c r="R28">
+      <c r="R28" t="n">
         <v>980.0833</v>
       </c>
-      <c r="S28">
+      <c r="S28" t="n">
         <v>628.1669000000001</v>
       </c>
-      <c r="T28">
+      <c r="T28" t="n">
         <v>564.2670000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>98.4409</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>133.0488</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>103.64</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>148.08</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>206.78</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>255.0522</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>165.8528</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>272.0397</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>264.3754</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>260.649</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>292.109</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>305.1076</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>274.0216</v>
       </c>
-      <c r="O29">
+      <c r="O29" t="n">
         <v>259.5816</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="n">
         <v>259.0493</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" t="n">
         <v>176.8471</v>
       </c>
-      <c r="R29">
+      <c r="R29" t="n">
         <v>80.2634</v>
       </c>
-      <c r="S29">
+      <c r="S29" t="n">
         <v>96.3608</v>
       </c>
-      <c r="T29">
+      <c r="T29" t="n">
         <v>93.0652</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30">
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>584.0605</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>782.9108</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>722.27</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>1202.12</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>1523.24</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>1663.9672</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>1379.1281</v>
       </c>
-      <c r="I30">
+      <c r="I30" t="n">
         <v>1496.3445</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>1514.1458</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>1583.5321</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>1866.4963</v>
       </c>
-      <c r="M30">
+      <c r="M30" t="n">
         <v>2105.939</v>
       </c>
-      <c r="N30">
+      <c r="N30" t="n">
         <v>2141.1228</v>
       </c>
-      <c r="O30">
+      <c r="O30" t="n">
         <v>1903.8958</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="n">
         <v>1635.7832</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" t="n">
         <v>1238.5562</v>
       </c>
-      <c r="R30">
+      <c r="R30" t="n">
         <v>1114.7675</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>1045.5123</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>1016.7423</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31">
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>355.6249</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>408.2936</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>389.54</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>760.45</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>733.55</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>714.6541999999999</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>948.4657999999999</v>
       </c>
-      <c r="I31">
+      <c r="I31" t="n">
         <v>1145.7094</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>789.9455</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>789.7947</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>826.2138</v>
       </c>
-      <c r="M31">
+      <c r="M31" t="n">
         <v>868.9791</v>
       </c>
-      <c r="N31">
+      <c r="N31" t="n">
         <v>943.2852</v>
       </c>
-      <c r="O31">
+      <c r="O31" t="n">
         <v>869.4048</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="n">
         <v>1105.7628</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" t="n">
         <v>1185.5168</v>
       </c>
-      <c r="R31">
+      <c r="R31" t="n">
         <v>695.6295</v>
       </c>
-      <c r="S31">
+      <c r="S31" t="n">
         <v>412.0592</v>
       </c>
-      <c r="T31">
+      <c r="T31" t="n">
         <v>443.3349</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32">
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>753.9298</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>1005.1959</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>658.49</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>1083.33</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>1428.61</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>1306.3772</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>1226.1821</v>
       </c>
-      <c r="I32">
+      <c r="I32" t="n">
         <v>1313.4782</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>1293.2831</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>1695.2057</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>2571.443</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="n">
         <v>2735.3749</v>
       </c>
-      <c r="N32">
+      <c r="N32" t="n">
         <v>3330.5664</v>
       </c>
-      <c r="O32">
+      <c r="O32" t="n">
         <v>3241.9735</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="n">
         <v>3025.6836</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" t="n">
         <v>2480.0061</v>
       </c>
-      <c r="R32">
+      <c r="R32" t="n">
         <v>1865.2396</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>1823.1275</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>1742.3257</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33">
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>2011.703</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>3310.1292</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>2669.93</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>3771.22</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>3986.31</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>4063.4236</v>
       </c>
-      <c r="H33">
+      <c r="H33" t="n">
         <v>4105.1083</v>
       </c>
-      <c r="I33">
+      <c r="I33" t="n">
         <v>4359.1906</v>
       </c>
-      <c r="J33">
+      <c r="J33" t="n">
         <v>4423.6751</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="n">
         <v>4477.7122</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>5105.4642</v>
       </c>
-      <c r="M33">
+      <c r="M33" t="n">
         <v>5452.6452</v>
       </c>
-      <c r="N33">
+      <c r="N33" t="n">
         <v>5424.7646</v>
       </c>
-      <c r="O33">
+      <c r="O33" t="n">
         <v>5149.0817</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="n">
         <v>4814.4922</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" t="n">
         <v>4945.416</v>
       </c>
-      <c r="R33">
+      <c r="R33" t="n">
         <v>2723.0234</v>
       </c>
-      <c r="S33">
+      <c r="S33" t="n">
         <v>2258.0569</v>
       </c>
-      <c r="T33">
+      <c r="T33" t="n">
         <v>1925.6251</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34">
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>212.2323</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>294.1956</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>269.39</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>442.97</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>497.98</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>384.0193</v>
       </c>
-      <c r="H34">
+      <c r="H34" t="n">
         <v>388.3346</v>
       </c>
-      <c r="I34">
+      <c r="I34" t="n">
         <v>543.0865</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>614.0135</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>454.4622</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>492.8382</v>
       </c>
-      <c r="M34">
+      <c r="M34" t="n">
         <v>519.9868</v>
       </c>
-      <c r="N34">
+      <c r="N34" t="n">
         <v>529.1999</v>
       </c>
-      <c r="O34">
+      <c r="O34" t="n">
         <v>606.1611</v>
       </c>
-      <c r="P34">
+      <c r="P34" t="n">
         <v>674.2043</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" t="n">
         <v>528.1975</v>
       </c>
-      <c r="R34">
+      <c r="R34" t="n">
         <v>365.1675</v>
       </c>
-      <c r="S34">
+      <c r="S34" t="n">
         <v>324.4394</v>
       </c>
-      <c r="T34">
+      <c r="T34" t="n">
         <v>225.7552</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35">
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>369.9679</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>472.9936</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>516.65</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>653.91</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>786.1900000000001</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>785.9371</v>
       </c>
-      <c r="H35">
+      <c r="H35" t="n">
         <v>775.1944999999999</v>
       </c>
-      <c r="I35">
+      <c r="I35" t="n">
         <v>762.5025000000001</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>663.35</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>701.7822</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>834.4948000000001</v>
       </c>
-      <c r="M35">
+      <c r="M35" t="n">
         <v>951.8339</v>
       </c>
-      <c r="N35">
+      <c r="N35" t="n">
         <v>1116.0847</v>
       </c>
-      <c r="O35">
+      <c r="O35" t="n">
         <v>1156.1255</v>
       </c>
-      <c r="P35">
+      <c r="P35" t="n">
         <v>936.3943</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" t="n">
         <v>930.2065</v>
       </c>
-      <c r="R35">
+      <c r="R35" t="n">
         <v>470.3054</v>
       </c>
-      <c r="S35">
+      <c r="S35" t="n">
         <v>534.1412</v>
       </c>
-      <c r="T35">
+      <c r="T35" t="n">
         <v>491.8142</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36">
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>693.9136999999999</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>928.5126</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>802.27</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>1357.95</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>1624.04</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>1394.1771</v>
       </c>
-      <c r="H36">
+      <c r="H36" t="n">
         <v>1385.3288</v>
       </c>
-      <c r="I36">
+      <c r="I36" t="n">
         <v>1659.5284</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>1331.3566</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>1687.0641</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>2308.2361</v>
       </c>
-      <c r="M36">
+      <c r="M36" t="n">
         <v>1823.8103</v>
       </c>
-      <c r="N36">
+      <c r="N36" t="n">
         <v>1973.3443</v>
       </c>
-      <c r="O36">
+      <c r="O36" t="n">
         <v>2005.9086</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="n">
         <v>2046.5513</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" t="n">
         <v>2304.8639</v>
       </c>
-      <c r="R36">
+      <c r="R36" t="n">
         <v>1472.97</v>
       </c>
-      <c r="S36">
+      <c r="S36" t="n">
         <v>1363.0608</v>
       </c>
-      <c r="T36">
+      <c r="T36" t="n">
         <v>1097.5019</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37">
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>645.0209</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>769.732</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>686.22</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>1151.15</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>1209.87</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>919.4949</v>
       </c>
-      <c r="H37">
+      <c r="H37" t="n">
         <v>842.4978</v>
       </c>
-      <c r="I37">
+      <c r="I37" t="n">
         <v>1050.6059</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="n">
         <v>1022.2752</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="n">
         <v>1238.9898</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>1752.0805</v>
       </c>
-      <c r="M37">
+      <c r="M37" t="n">
         <v>1633.8365</v>
       </c>
-      <c r="N37">
+      <c r="N37" t="n">
         <v>1578.3054</v>
       </c>
-      <c r="O37">
+      <c r="O37" t="n">
         <v>1475.5787</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="n">
         <v>1430.3733</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" t="n">
         <v>1419.6327</v>
       </c>
-      <c r="R37">
+      <c r="R37" t="n">
         <v>1264.0756</v>
       </c>
-      <c r="S37">
+      <c r="S37" t="n">
         <v>1209.6428</v>
       </c>
-      <c r="T37">
+      <c r="T37" t="n">
         <v>925.0821999999999</v>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>